--- a/output/yearly_benthic_cover_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_69_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.32745757604787</v>
+        <v>45.30912035273587</v>
       </c>
       <c r="M2" t="n">
-        <v>99.4122842869597</v>
+        <v>100.2066923817708</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98331147647734</v>
+        <v>87.98897616073081</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93376545854208</v>
+        <v>45.88614285453986</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22861384481693</v>
+        <v>2.228664520703493</v>
       </c>
       <c r="E3" t="n">
-        <v>5.706741064593196</v>
+        <v>5.680049320457416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428712816056433</v>
+        <v>0.7428881735678312</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97536782793446</v>
+        <v>33.95873905687338</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17207895385959</v>
+        <v>34.17285598412023</v>
       </c>
       <c r="I3" t="n">
-        <v>6.514692993632236</v>
+        <v>6.562728020209524</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642945510035271</v>
+        <v>4.643051084798945</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01668852352267</v>
+        <v>12.01102383926917</v>
       </c>
       <c r="L3" t="n">
-        <v>48.81568969477605</v>
+        <v>48.86725803824933</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7661436768408</v>
+        <v>106.7644247320584</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.91906365651153</v>
+        <v>86.99378812286363</v>
       </c>
       <c r="C4" t="n">
-        <v>42.49416467032223</v>
+        <v>42.52664303654181</v>
       </c>
       <c r="D4" t="n">
-        <v>2.176553723390811</v>
+        <v>2.180258028974924</v>
       </c>
       <c r="E4" t="n">
-        <v>6.48013857131418</v>
+        <v>6.470082975777639</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444211510579735</v>
+        <v>0.7444481862860938</v>
       </c>
       <c r="G4" t="n">
-        <v>33.18170777833326</v>
+        <v>33.22115679359479</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24337294866677</v>
+        <v>34.24461656916031</v>
       </c>
       <c r="I4" t="n">
-        <v>5.440237289636197</v>
+        <v>5.480424404781804</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652632194112335</v>
+        <v>4.652801164288086</v>
       </c>
       <c r="K4" t="n">
-        <v>13.08093634348848</v>
+        <v>13.00621187713636</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24393529192172</v>
+        <v>44.28484708576045</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81903630573242</v>
+        <v>99.81770199943861</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.42824457708497</v>
+        <v>85.77899814784763</v>
       </c>
       <c r="C5" t="n">
-        <v>41.84759065711915</v>
+        <v>42.16232606583714</v>
       </c>
       <c r="D5" t="n">
-        <v>2.102716619565613</v>
+        <v>2.12076742581546</v>
       </c>
       <c r="E5" t="n">
-        <v>7.017234731620194</v>
+        <v>7.056063370984263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457403232458238</v>
+        <v>0.7457717249565591</v>
       </c>
       <c r="G5" t="n">
-        <v>32.05605616863657</v>
+        <v>32.31468305101886</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30405486930789</v>
+        <v>34.30549934800172</v>
       </c>
       <c r="I5" t="n">
-        <v>4.541564844422471</v>
+        <v>4.575139946092285</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660877020286399</v>
+        <v>4.661073280978494</v>
       </c>
       <c r="K5" t="n">
-        <v>14.57175542291502</v>
+        <v>14.22100185215237</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42953621747594</v>
+        <v>43.46443807076657</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84888229751012</v>
+        <v>99.84776598875607</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.85135656634631</v>
+        <v>84.37563235211505</v>
       </c>
       <c r="C6" t="n">
-        <v>40.97563272738823</v>
+        <v>41.46935588066648</v>
       </c>
       <c r="D6" t="n">
-        <v>2.025237364925689</v>
+        <v>2.052127725321554</v>
       </c>
       <c r="E6" t="n">
-        <v>7.390392488235648</v>
+        <v>7.464084990144862</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468639820044541</v>
+        <v>0.7468967064701514</v>
       </c>
       <c r="G6" t="n">
-        <v>30.87487972501548</v>
+        <v>31.26880214056278</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35574317220488</v>
+        <v>34.35724849762696</v>
       </c>
       <c r="I6" t="n">
-        <v>3.790339946432331</v>
+        <v>3.818367876550296</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667899887527839</v>
+        <v>4.668104415438446</v>
       </c>
       <c r="K6" t="n">
-        <v>16.14864343365367</v>
+        <v>15.62436764788496</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74956925994635</v>
+        <v>42.77918925072378</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87384542098825</v>
+        <v>99.87291277927523</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81.98517213086306</v>
+        <v>82.80979938524101</v>
       </c>
       <c r="C7" t="n">
-        <v>39.69762522836918</v>
+        <v>40.4964074673684</v>
       </c>
       <c r="D7" t="n">
-        <v>1.933915566033141</v>
+        <v>1.975872467870543</v>
       </c>
       <c r="E7" t="n">
-        <v>7.584258690126119</v>
+        <v>7.717735178243658</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478243550315786</v>
+        <v>0.7478545855654641</v>
       </c>
       <c r="G7" t="n">
-        <v>29.48267276403886</v>
+        <v>30.10688101450825</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39992033145261</v>
+        <v>34.40131093601135</v>
       </c>
       <c r="I7" t="n">
-        <v>3.162678205233406</v>
+        <v>3.186054043257589</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673902218947367</v>
+        <v>4.674091159784151</v>
       </c>
       <c r="K7" t="n">
-        <v>18.01482786913692</v>
+        <v>17.190200614759</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18225968175966</v>
+        <v>42.20732614352399</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89471277926577</v>
+        <v>99.89393422565138</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86.86799057099012</v>
+        <v>87.71756431734747</v>
       </c>
       <c r="C8" t="n">
-        <v>41.98484114433668</v>
+        <v>42.79337987141491</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9380965620675</v>
+        <v>1.980131503132992</v>
       </c>
       <c r="E8" t="n">
-        <v>9.407662799417553</v>
+        <v>9.549416623239241</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749441101242065</v>
+        <v>0.7494666020811555</v>
       </c>
       <c r="G8" t="n">
-        <v>29.98040909849953</v>
+        <v>30.60660718632991</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47429065713498</v>
+        <v>34.47546369573315</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6340834698656</v>
+        <v>5.672312443823778</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684006882762906</v>
+        <v>4.684166263007222</v>
       </c>
       <c r="K8" t="n">
-        <v>13.13200942900986</v>
+        <v>12.28243568265255</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69575178548398</v>
+        <v>44.73551404754103</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81260235883053</v>
+        <v>99.81132960160849</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.57029344470571</v>
+        <v>85.7497608612323</v>
       </c>
       <c r="C9" t="n">
-        <v>40.56042402797911</v>
+        <v>41.70563963142147</v>
       </c>
       <c r="D9" t="n">
-        <v>1.833733600062154</v>
+        <v>1.891132181490492</v>
       </c>
       <c r="E9" t="n">
-        <v>9.685039692360002</v>
+        <v>9.909478397199138</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508305574960655</v>
+        <v>0.7508462737817575</v>
       </c>
       <c r="G9" t="n">
-        <v>28.36601879572035</v>
+        <v>29.23095750192666</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53820564481901</v>
+        <v>34.53892859396084</v>
       </c>
       <c r="I9" t="n">
-        <v>4.703774169897724</v>
+        <v>4.735628701737434</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69269098435041</v>
+        <v>4.692789211135985</v>
       </c>
       <c r="K9" t="n">
-        <v>15.42970655529429</v>
+        <v>14.25023913876768</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85336709811922</v>
+        <v>43.88655699526019</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84349768139262</v>
+        <v>99.84243576544932</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.15835005258546</v>
+        <v>83.63741672053028</v>
       </c>
       <c r="C10" t="n">
-        <v>38.87698122155966</v>
+        <v>40.32779642227066</v>
       </c>
       <c r="D10" t="n">
-        <v>1.725586955571913</v>
+        <v>1.796600598694758</v>
       </c>
       <c r="E10" t="n">
-        <v>9.768195429025424</v>
+        <v>10.07289792672486</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520265416397542</v>
+        <v>0.7520290679113948</v>
       </c>
       <c r="G10" t="n">
-        <v>26.69309872150657</v>
+        <v>27.76979645441379</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59322091542869</v>
+        <v>34.59333712392415</v>
       </c>
       <c r="I10" t="n">
-        <v>3.926055604164644</v>
+        <v>3.952573874415109</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700165885248465</v>
+        <v>4.700181674446218</v>
       </c>
       <c r="K10" t="n">
-        <v>17.84164994741455</v>
+        <v>16.3625832794697</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15070843741752</v>
+        <v>43.17807505654469</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86933960639172</v>
+        <v>99.86845475828505</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.68697050570101</v>
+        <v>81.32482470646863</v>
       </c>
       <c r="C11" t="n">
-        <v>37.01281360143764</v>
+        <v>38.62770062735193</v>
       </c>
       <c r="D11" t="n">
-        <v>1.616122149222486</v>
+        <v>1.694072414930927</v>
       </c>
       <c r="E11" t="n">
-        <v>9.694570294559719</v>
+        <v>10.04776975518358</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530571521487689</v>
+        <v>0.7530457278443861</v>
       </c>
       <c r="G11" t="n">
-        <v>24.99978800599562</v>
+        <v>26.18503309853446</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64062899884336</v>
+        <v>34.64010348084175</v>
       </c>
       <c r="I11" t="n">
-        <v>3.276196704001245</v>
+        <v>3.298264430106137</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706607200929807</v>
+        <v>4.706535799027414</v>
       </c>
       <c r="K11" t="n">
-        <v>20.31302949429899</v>
+        <v>18.67517529353135</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56509980414769</v>
+        <v>42.58733036038296</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89094289988432</v>
+        <v>99.89020628126625</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.24011981198191</v>
+        <v>78.95789926093629</v>
       </c>
       <c r="C12" t="n">
-        <v>35.07171422820768</v>
+        <v>36.77108783292016</v>
       </c>
       <c r="D12" t="n">
-        <v>1.508994608522306</v>
+        <v>1.590194588449704</v>
       </c>
       <c r="E12" t="n">
-        <v>9.50751247461181</v>
+        <v>9.890280937130603</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539454619644944</v>
+        <v>0.7539205362729534</v>
       </c>
       <c r="G12" t="n">
-        <v>23.34263244482926</v>
+        <v>24.57940850973815</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68149125036673</v>
+        <v>34.68034466855585</v>
       </c>
       <c r="I12" t="n">
-        <v>2.733384434409215</v>
+        <v>2.751746669083065</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712159137278091</v>
+        <v>4.71200335170596</v>
       </c>
       <c r="K12" t="n">
-        <v>22.75988018801808</v>
+        <v>21.04210073906372</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07740011977421</v>
+        <v>42.09519297162428</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90899453599997</v>
+        <v>99.90838154360816</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.81656522910643</v>
+        <v>76.49965381908943</v>
       </c>
       <c r="C13" t="n">
-        <v>33.06916713405367</v>
+        <v>34.7377461671172</v>
       </c>
       <c r="D13" t="n">
-        <v>1.403981064294382</v>
+        <v>1.483271184895502</v>
       </c>
       <c r="E13" t="n">
-        <v>9.225890632165118</v>
+        <v>9.607835706874098</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547113783270575</v>
+        <v>0.7546745968050844</v>
       </c>
       <c r="G13" t="n">
-        <v>21.71817828787128</v>
+        <v>22.92670887517802</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71672340304464</v>
+        <v>34.71503145303388</v>
       </c>
       <c r="I13" t="n">
-        <v>2.280134348859852</v>
+        <v>2.295415772271065</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71694611454411</v>
+        <v>4.716716230031778</v>
       </c>
       <c r="K13" t="n">
-        <v>25.18343477089356</v>
+        <v>23.50034618091058</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67147074965251</v>
+        <v>41.6854702444977</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92407265459974</v>
+        <v>99.92356259252549</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.32500703182214</v>
+        <v>83.33810194026552</v>
       </c>
       <c r="C14" t="n">
-        <v>37.76585350512957</v>
+        <v>38.9792404583729</v>
       </c>
       <c r="D14" t="n">
-        <v>1.405654923157962</v>
+        <v>1.485036707318251</v>
       </c>
       <c r="E14" t="n">
-        <v>11.81659021615526</v>
+        <v>11.97314169995638</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556111627772788</v>
+        <v>0.7555728782091234</v>
       </c>
       <c r="G14" t="n">
-        <v>23.8330225315409</v>
+        <v>24.8118857615587</v>
       </c>
       <c r="H14" t="n">
-        <v>36.84706481438127</v>
+        <v>36.61423985843127</v>
       </c>
       <c r="I14" t="n">
-        <v>2.944493616451462</v>
+        <v>2.975894545984784</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722569767357993</v>
+        <v>4.722330488807022</v>
       </c>
       <c r="K14" t="n">
-        <v>17.67499296817788</v>
+        <v>16.66189805973447</v>
       </c>
       <c r="L14" t="n">
-        <v>44.46112061659191</v>
+        <v>44.25978292920783</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90196708989936</v>
+        <v>99.9009214473152</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.62320468544129</v>
+        <v>82.58716312128715</v>
       </c>
       <c r="C15" t="n">
-        <v>37.51803393397994</v>
+        <v>38.68801691500639</v>
       </c>
       <c r="D15" t="n">
-        <v>1.380416007433891</v>
+        <v>1.457355883716192</v>
       </c>
       <c r="E15" t="n">
-        <v>12.01378778948686</v>
+        <v>12.16369724329874</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563690912941822</v>
+        <v>0.7563299093825568</v>
       </c>
       <c r="G15" t="n">
-        <v>23.40509414228014</v>
+        <v>24.34939656542265</v>
       </c>
       <c r="H15" t="n">
-        <v>36.88402488400803</v>
+        <v>36.65092476569011</v>
       </c>
       <c r="I15" t="n">
-        <v>2.456205950349549</v>
+        <v>2.482396820135909</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727306820588639</v>
+        <v>4.72706193364098</v>
       </c>
       <c r="K15" t="n">
-        <v>18.37679531455871</v>
+        <v>17.41283687871285</v>
       </c>
       <c r="L15" t="n">
-        <v>44.02337926211548</v>
+        <v>43.81648246889228</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91820851065413</v>
+        <v>99.91733626261153</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.17262497096266</v>
+        <v>80.16040060611354</v>
       </c>
       <c r="C16" t="n">
-        <v>35.44622703134277</v>
+        <v>36.64479442277651</v>
       </c>
       <c r="D16" t="n">
-        <v>1.289601140684677</v>
+        <v>1.365388073433963</v>
       </c>
       <c r="E16" t="n">
-        <v>11.56485815974037</v>
+        <v>11.7411698925575</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570214634660976</v>
+        <v>0.7569810785828133</v>
       </c>
       <c r="G16" t="n">
-        <v>21.86531881778559</v>
+        <v>22.81280505140942</v>
       </c>
       <c r="H16" t="n">
-        <v>36.91583754227172</v>
+        <v>36.68247971687249</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0486037003511</v>
+        <v>2.070445052114763</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73138414666311</v>
+        <v>4.731131741142583</v>
       </c>
       <c r="K16" t="n">
-        <v>20.82737502903734</v>
+        <v>19.83959939388646</v>
       </c>
       <c r="L16" t="n">
-        <v>43.65816999655462</v>
+        <v>43.44665071611102</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93177205693473</v>
+        <v>99.931044532774</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.13731811165546</v>
+        <v>81.88127670445665</v>
       </c>
       <c r="C17" t="n">
-        <v>36.86244573558294</v>
+        <v>37.89885206371661</v>
       </c>
       <c r="D17" t="n">
-        <v>1.290681070939592</v>
+        <v>1.366534393792822</v>
       </c>
       <c r="E17" t="n">
-        <v>12.43780984008314</v>
+        <v>12.53465431775491</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576554039584138</v>
+        <v>0.7576166069271234</v>
       </c>
       <c r="G17" t="n">
-        <v>22.4071685546031</v>
+        <v>23.27186497080216</v>
       </c>
       <c r="H17" t="n">
-        <v>37.47029079657226</v>
+        <v>37.15318401103977</v>
       </c>
       <c r="I17" t="n">
-        <v>2.038366170758874</v>
+        <v>2.062318610845342</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735346274740087</v>
+        <v>4.735103793294521</v>
       </c>
       <c r="K17" t="n">
-        <v>18.86268188834454</v>
+        <v>18.11872329554335</v>
       </c>
       <c r="L17" t="n">
-        <v>44.20698368799587</v>
+        <v>43.91373835306078</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93211131192335</v>
+        <v>99.93131371232074</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.66481597094099</v>
+        <v>79.57750754167108</v>
       </c>
       <c r="C18" t="n">
-        <v>34.70391914147518</v>
+        <v>35.91333426688664</v>
       </c>
       <c r="D18" t="n">
-        <v>1.20323515226172</v>
+        <v>1.282768003455678</v>
       </c>
       <c r="E18" t="n">
-        <v>11.87843662271915</v>
+        <v>12.05293938203411</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582011412171205</v>
+        <v>0.7581623964167513</v>
       </c>
       <c r="G18" t="n">
-        <v>20.88904336988898</v>
+        <v>21.84533656882982</v>
       </c>
       <c r="H18" t="n">
-        <v>37.49728055164485</v>
+        <v>37.17994928671355</v>
       </c>
       <c r="I18" t="n">
-        <v>1.699862000602167</v>
+        <v>1.719836926616469</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738757132607004</v>
+        <v>4.738514977604696</v>
       </c>
       <c r="K18" t="n">
-        <v>21.335184029059</v>
+        <v>20.42249245832891</v>
       </c>
       <c r="L18" t="n">
-        <v>43.90427554694474</v>
+        <v>43.60688664670541</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94337871747894</v>
+        <v>99.94271337192097</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.72721746095418</v>
+        <v>78.64763538611668</v>
       </c>
       <c r="C19" t="n">
-        <v>34.02714764853272</v>
+        <v>35.2482004349898</v>
       </c>
       <c r="D19" t="n">
-        <v>1.17072617247055</v>
+        <v>1.249622153045975</v>
       </c>
       <c r="E19" t="n">
-        <v>11.79378306999399</v>
+        <v>11.98051107152773</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586621022169303</v>
+        <v>0.7586232099496746</v>
       </c>
       <c r="G19" t="n">
-        <v>20.32466367445527</v>
+        <v>21.28086796959019</v>
       </c>
       <c r="H19" t="n">
-        <v>37.52007764728822</v>
+        <v>37.20254737897675</v>
       </c>
       <c r="I19" t="n">
-        <v>1.417666655673396</v>
+        <v>1.434068540840896</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741638138855816</v>
+        <v>4.741395062185466</v>
       </c>
       <c r="K19" t="n">
-        <v>22.27278253904583</v>
+        <v>21.35236461388332</v>
       </c>
       <c r="L19" t="n">
-        <v>43.65284296957726</v>
+        <v>43.35166170316531</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9527731571558</v>
+        <v>99.95222675203843</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.09272694903896</v>
+        <v>76.21720113452919</v>
       </c>
       <c r="C20" t="n">
-        <v>31.61024265384286</v>
+        <v>33.03836633875397</v>
       </c>
       <c r="D20" t="n">
-        <v>1.07864107158022</v>
+        <v>1.162225063582332</v>
       </c>
       <c r="E20" t="n">
-        <v>11.06312806075046</v>
+        <v>11.34188869491239</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590601635084592</v>
+        <v>0.7590199148657922</v>
       </c>
       <c r="G20" t="n">
-        <v>18.7259988892693</v>
+        <v>19.79250933472704</v>
       </c>
       <c r="H20" t="n">
-        <v>37.5397640010983</v>
+        <v>37.22200161296772</v>
       </c>
       <c r="I20" t="n">
-        <v>1.182008740904352</v>
+        <v>1.195682045562706</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744126021927871</v>
+        <v>4.743874467911202</v>
       </c>
       <c r="K20" t="n">
-        <v>24.90727305096102</v>
+        <v>23.78279886547082</v>
       </c>
       <c r="L20" t="n">
-        <v>43.44310466587187</v>
+        <v>43.13899955852963</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96062037067576</v>
+        <v>99.96016476275443</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.1969691021655</v>
+        <v>82.08398797042953</v>
       </c>
       <c r="C21" t="n">
-        <v>35.43209922422321</v>
+        <v>36.66800628387855</v>
       </c>
       <c r="D21" t="n">
-        <v>1.079377262307152</v>
+        <v>1.163042349372529</v>
       </c>
       <c r="E21" t="n">
-        <v>13.11315868547704</v>
+        <v>13.30162142120799</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595782348746272</v>
+        <v>0.7595536636295511</v>
       </c>
       <c r="G21" t="n">
-        <v>20.50416804698843</v>
+        <v>21.46957407959487</v>
       </c>
       <c r="H21" t="n">
-        <v>39.33077387087535</v>
+        <v>38.91132291365741</v>
       </c>
       <c r="I21" t="n">
-        <v>1.662549033676482</v>
+        <v>1.731663145282482</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747363967966421</v>
+        <v>4.747210397684696</v>
       </c>
       <c r="K21" t="n">
-        <v>18.8030308978345</v>
+        <v>17.91601202957047</v>
       </c>
       <c r="L21" t="n">
-        <v>45.70948937494722</v>
+        <v>45.35830014382198</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94461949700494</v>
+        <v>99.942318457271</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_69_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.30912035273587</v>
+        <v>44.79724235780715</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2066923817708</v>
+        <v>101.8701008820861</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98897616073081</v>
+        <v>88.0537715092111</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88614285453986</v>
+        <v>45.93486515232468</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228664520703493</v>
+        <v>2.22879379271933</v>
       </c>
       <c r="E3" t="n">
-        <v>5.680049320457416</v>
+        <v>5.711345717480888</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428881735678312</v>
+        <v>0.7429312642397768</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95873905687338</v>
+        <v>33.97498852593531</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17285598412023</v>
+        <v>34.17483815502973</v>
       </c>
       <c r="I3" t="n">
-        <v>6.562728020209524</v>
+        <v>6.577553652307477</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643051084798945</v>
+        <v>4.643320401498605</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01102383926917</v>
+        <v>11.94622849078888</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86725803824933</v>
+        <v>48.88281260343849</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7644247320584</v>
+        <v>106.7639062465521</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99378812286363</v>
+        <v>87.2189892816767</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52664303654181</v>
+        <v>42.73682619121693</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180258028974924</v>
+        <v>2.188990692124298</v>
       </c>
       <c r="E4" t="n">
-        <v>6.470082975777639</v>
+        <v>6.524816046659398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444481862860938</v>
+        <v>0.7444908534264624</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22115679359479</v>
+        <v>33.36824334814885</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24461656916031</v>
+        <v>34.24657925761727</v>
       </c>
       <c r="I4" t="n">
-        <v>5.480424404781804</v>
+        <v>5.492801249785026</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652801164288086</v>
+        <v>4.65306783391539</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00621187713636</v>
+        <v>12.7810107183233</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28484708576045</v>
+        <v>44.29945326678457</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81770199943861</v>
+        <v>99.8172901763248</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.77899814784763</v>
+        <v>86.12129015230245</v>
       </c>
       <c r="C5" t="n">
-        <v>42.16232606583714</v>
+        <v>42.49173087345491</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12076742581546</v>
+        <v>2.135675144145167</v>
       </c>
       <c r="E5" t="n">
-        <v>7.056063370984263</v>
+        <v>7.130139207217817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457717249565591</v>
+        <v>0.7458121804854116</v>
       </c>
       <c r="G5" t="n">
-        <v>32.31468305101886</v>
+        <v>32.55551893337253</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30549934800172</v>
+        <v>34.30736030232894</v>
       </c>
       <c r="I5" t="n">
-        <v>4.575139946092285</v>
+        <v>4.585458256718764</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661073280978494</v>
+        <v>4.661326128033823</v>
       </c>
       <c r="K5" t="n">
-        <v>14.22100185215237</v>
+        <v>13.87870984769755</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46443807076657</v>
+        <v>43.47698146635352</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84776598875607</v>
+        <v>99.84742218750598</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.37563235211505</v>
+        <v>84.91994552158431</v>
       </c>
       <c r="C6" t="n">
-        <v>41.46935588066648</v>
+        <v>42.00267003682482</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052127725321554</v>
+        <v>2.077442520499378</v>
       </c>
       <c r="E6" t="n">
-        <v>7.464084990144862</v>
+        <v>7.573550369699363</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468967064701514</v>
+        <v>0.7469325258153166</v>
       </c>
       <c r="G6" t="n">
-        <v>31.26880214056278</v>
+        <v>31.6678402586276</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35724849762696</v>
+        <v>34.35889618750456</v>
       </c>
       <c r="I6" t="n">
-        <v>3.818367876550296</v>
+        <v>3.826955373092354</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668104415438446</v>
+        <v>4.668328286345729</v>
       </c>
       <c r="K6" t="n">
-        <v>15.62436764788496</v>
+        <v>15.08005447841571</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77918925072378</v>
+        <v>42.78990164429506</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87291277927523</v>
+        <v>99.87262615953559</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.80979938524101</v>
+        <v>83.54438517833</v>
       </c>
       <c r="C7" t="n">
-        <v>40.4964074673684</v>
+        <v>41.22172691098353</v>
       </c>
       <c r="D7" t="n">
-        <v>1.975872467870543</v>
+        <v>2.010840275811118</v>
       </c>
       <c r="E7" t="n">
-        <v>7.717735178243658</v>
+        <v>7.862943160422263</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478545855654641</v>
+        <v>0.7478841554594061</v>
       </c>
       <c r="G7" t="n">
-        <v>30.10688101450825</v>
+        <v>30.65257787478709</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40131093601135</v>
+        <v>34.40267115113269</v>
       </c>
       <c r="I7" t="n">
-        <v>3.186054043257589</v>
+        <v>3.193192589096157</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674091159784151</v>
+        <v>4.674275971621289</v>
       </c>
       <c r="K7" t="n">
-        <v>17.190200614759</v>
+        <v>16.45561482166999</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20732614352399</v>
+        <v>42.21635395142725</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89393422565138</v>
+        <v>99.89369568408077</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.71756431734747</v>
+        <v>88.48551641133636</v>
       </c>
       <c r="C8" t="n">
-        <v>42.79337987141491</v>
+        <v>43.5428680803285</v>
       </c>
       <c r="D8" t="n">
-        <v>1.980131503132992</v>
+        <v>2.015149442677872</v>
       </c>
       <c r="E8" t="n">
-        <v>9.549416623239241</v>
+        <v>9.711485418434556</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494666020811555</v>
+        <v>0.749486847459185</v>
       </c>
       <c r="G8" t="n">
-        <v>30.60660718632991</v>
+        <v>31.16005735556413</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47546369573315</v>
+        <v>34.47639498312252</v>
       </c>
       <c r="I8" t="n">
-        <v>5.672312443823778</v>
+        <v>5.688649567458183</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684166263007222</v>
+        <v>4.684292796619907</v>
       </c>
       <c r="K8" t="n">
-        <v>12.28243568265255</v>
+        <v>11.51448358866364</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73551404754103</v>
+        <v>44.75343216299968</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81132960160849</v>
+        <v>99.81078383199181</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.7497608612323</v>
+        <v>86.68747545727702</v>
       </c>
       <c r="C9" t="n">
-        <v>41.70563963142147</v>
+        <v>42.62822832777891</v>
       </c>
       <c r="D9" t="n">
-        <v>1.891132181490492</v>
+        <v>1.93418926446663</v>
       </c>
       <c r="E9" t="n">
-        <v>9.909478397199138</v>
+        <v>10.11285208677934</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508462737817575</v>
+        <v>0.7508555425698984</v>
       </c>
       <c r="G9" t="n">
-        <v>29.23095750192666</v>
+        <v>29.90817809383225</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53892859396084</v>
+        <v>34.53935495821533</v>
       </c>
       <c r="I9" t="n">
-        <v>4.735628701737434</v>
+        <v>4.749198370351698</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692789211135985</v>
+        <v>4.692847141061866</v>
       </c>
       <c r="K9" t="n">
-        <v>14.25023913876768</v>
+        <v>13.312524542723</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88655699526019</v>
+        <v>43.90122908595757</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84243576544932</v>
+        <v>99.84198195645948</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.63741672053028</v>
+        <v>84.70708658445668</v>
       </c>
       <c r="C10" t="n">
-        <v>40.32779642227066</v>
+        <v>41.38529699959889</v>
       </c>
       <c r="D10" t="n">
-        <v>1.796600598694758</v>
+        <v>1.845765386184198</v>
       </c>
       <c r="E10" t="n">
-        <v>10.07289792672486</v>
+        <v>10.31117018149147</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520290679113948</v>
+        <v>0.7520267433408087</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76979645441379</v>
+        <v>28.54088837301602</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59333712392415</v>
+        <v>34.59323019367721</v>
       </c>
       <c r="I10" t="n">
-        <v>3.952573874415109</v>
+        <v>3.963838560866924</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700181674446218</v>
+        <v>4.700167145880055</v>
       </c>
       <c r="K10" t="n">
-        <v>16.3625832794697</v>
+        <v>15.29291341554331</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17807505654469</v>
+        <v>43.18986740790362</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86845475828505</v>
+        <v>99.86807782304582</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.32482470646863</v>
+        <v>82.61107574919902</v>
       </c>
       <c r="C11" t="n">
-        <v>38.62770062735193</v>
+        <v>39.90437298222854</v>
       </c>
       <c r="D11" t="n">
-        <v>1.694072414930927</v>
+        <v>1.753041671255363</v>
       </c>
       <c r="E11" t="n">
-        <v>10.04776975518358</v>
+        <v>10.34444698274354</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530457278443861</v>
+        <v>0.7530304058283068</v>
       </c>
       <c r="G11" t="n">
-        <v>26.18503309853446</v>
+        <v>27.10711070163696</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64010348084175</v>
+        <v>34.63939866810212</v>
       </c>
       <c r="I11" t="n">
-        <v>3.298264430106137</v>
+        <v>3.307607283205793</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706535799027414</v>
+        <v>4.706440036426918</v>
       </c>
       <c r="K11" t="n">
-        <v>18.67517529353135</v>
+        <v>17.388924250801</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58733036038296</v>
+        <v>42.5965961402797</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89020628126625</v>
+        <v>99.88989337330923</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.95789926093629</v>
+        <v>80.30268323661591</v>
       </c>
       <c r="C12" t="n">
-        <v>36.77108783292016</v>
+        <v>38.10862714932632</v>
       </c>
       <c r="D12" t="n">
-        <v>1.590194588449704</v>
+        <v>1.651711226869334</v>
       </c>
       <c r="E12" t="n">
-        <v>9.890280937130603</v>
+        <v>10.20642670357129</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539205362729534</v>
+        <v>0.7538929693247318</v>
       </c>
       <c r="G12" t="n">
-        <v>24.57940850973815</v>
+        <v>25.54024802035729</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68034466855585</v>
+        <v>34.67907658893768</v>
       </c>
       <c r="I12" t="n">
-        <v>2.751746669083065</v>
+        <v>2.759496669276004</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71200335170596</v>
+        <v>4.711831058279574</v>
       </c>
       <c r="K12" t="n">
-        <v>21.04210073906372</v>
+        <v>19.6973167633841</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09519297162428</v>
+        <v>42.10217810720054</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90838154360816</v>
+        <v>99.90812201991096</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.49965381908943</v>
+        <v>77.82936165350294</v>
       </c>
       <c r="C13" t="n">
-        <v>34.7377461671172</v>
+        <v>36.06222076329802</v>
       </c>
       <c r="D13" t="n">
-        <v>1.483271184895502</v>
+        <v>1.543996871547371</v>
       </c>
       <c r="E13" t="n">
-        <v>9.607835706874098</v>
+        <v>9.924468164773362</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546745968050844</v>
+        <v>0.7546361964259152</v>
       </c>
       <c r="G13" t="n">
-        <v>22.92670887517802</v>
+        <v>23.87467155304092</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71503145303388</v>
+        <v>34.71326503559211</v>
       </c>
       <c r="I13" t="n">
-        <v>2.295415772271065</v>
+        <v>2.301847604461306</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716716230031778</v>
+        <v>4.716476227661969</v>
       </c>
       <c r="K13" t="n">
-        <v>23.50034618091058</v>
+        <v>22.17063834649706</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6854702444977</v>
+        <v>41.69048820494725</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92356259252549</v>
+        <v>99.92334731474233</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.33810194026552</v>
+        <v>84.23825659281238</v>
       </c>
       <c r="C14" t="n">
-        <v>38.9792404583729</v>
+        <v>39.96634910324666</v>
       </c>
       <c r="D14" t="n">
-        <v>1.485036707318251</v>
+        <v>1.545869254685917</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97314169995638</v>
+        <v>12.12852362110706</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555728782091234</v>
+        <v>0.7555513330534321</v>
       </c>
       <c r="G14" t="n">
-        <v>24.8118857615587</v>
+        <v>25.58487151991561</v>
       </c>
       <c r="H14" t="n">
-        <v>36.61423985843127</v>
+        <v>36.43660881127643</v>
       </c>
       <c r="I14" t="n">
-        <v>2.975894545984784</v>
+        <v>3.064636221189994</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722330488807022</v>
+        <v>4.72219583158395</v>
       </c>
       <c r="K14" t="n">
-        <v>16.66189805973447</v>
+        <v>15.76174340718761</v>
       </c>
       <c r="L14" t="n">
-        <v>44.25978292920783</v>
+        <v>44.16987668017691</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9009214473152</v>
+        <v>99.89796919061116</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.58716312128715</v>
+        <v>83.51016304291181</v>
       </c>
       <c r="C15" t="n">
-        <v>38.68801691500639</v>
+        <v>39.70867145461086</v>
       </c>
       <c r="D15" t="n">
-        <v>1.457355883716192</v>
+        <v>1.51831120843492</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16369724329874</v>
+        <v>12.34208639490023</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563299093825568</v>
+        <v>0.7563223146507998</v>
       </c>
       <c r="G15" t="n">
-        <v>24.34939656542265</v>
+        <v>25.13247115932704</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65092476569011</v>
+        <v>36.47748796151946</v>
       </c>
       <c r="I15" t="n">
-        <v>2.482396820135909</v>
+        <v>2.556469537511864</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72706193364098</v>
+        <v>4.727014466567498</v>
       </c>
       <c r="K15" t="n">
-        <v>17.41283687871285</v>
+        <v>16.48983695708817</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81648246889228</v>
+        <v>43.71636280437902</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91733626261153</v>
+        <v>99.91487121607805</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.16040060611354</v>
+        <v>81.09250132895659</v>
       </c>
       <c r="C16" t="n">
-        <v>36.64479442277651</v>
+        <v>37.68659457690107</v>
       </c>
       <c r="D16" t="n">
-        <v>1.365388073433963</v>
+        <v>1.425420116115933</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7411698925575</v>
+        <v>11.94236736204267</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569810785828133</v>
+        <v>0.7569852097662545</v>
       </c>
       <c r="G16" t="n">
-        <v>22.81280505140942</v>
+        <v>23.59485312311967</v>
       </c>
       <c r="H16" t="n">
-        <v>36.68247971687249</v>
+        <v>36.50945944791533</v>
       </c>
       <c r="I16" t="n">
-        <v>2.070445052114763</v>
+        <v>2.132258508957653</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731131741142583</v>
+        <v>4.73115756103909</v>
       </c>
       <c r="K16" t="n">
-        <v>19.83959939388646</v>
+        <v>18.90749867104341</v>
       </c>
       <c r="L16" t="n">
-        <v>43.44665071611102</v>
+        <v>43.33489370934685</v>
       </c>
       <c r="M16" t="n">
-        <v>99.931044532774</v>
+        <v>99.92898695729133</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.88127670445665</v>
+        <v>82.76212037966097</v>
       </c>
       <c r="C17" t="n">
-        <v>37.89885206371661</v>
+        <v>38.89118961823893</v>
       </c>
       <c r="D17" t="n">
-        <v>1.366534393792822</v>
+        <v>1.426656737930027</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53465431775491</v>
+        <v>12.71851853867714</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576166069271234</v>
+        <v>0.7576419315374434</v>
       </c>
       <c r="G17" t="n">
-        <v>23.27186497080216</v>
+        <v>24.0221124232415</v>
       </c>
       <c r="H17" t="n">
-        <v>37.15318401103977</v>
+        <v>36.9479228020007</v>
       </c>
       <c r="I17" t="n">
-        <v>2.062318610845342</v>
+        <v>2.15400587416513</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735103793294521</v>
+        <v>4.735262072109021</v>
       </c>
       <c r="K17" t="n">
-        <v>18.11872329554335</v>
+        <v>17.23787962033903</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91373835306078</v>
+        <v>43.79919280181256</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93131371232074</v>
+        <v>99.92826204039052</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.57750754167108</v>
+        <v>80.46647027038951</v>
       </c>
       <c r="C18" t="n">
-        <v>35.91333426688664</v>
+        <v>36.9284470046376</v>
       </c>
       <c r="D18" t="n">
-        <v>1.282768003455678</v>
+        <v>1.341845304096138</v>
       </c>
       <c r="E18" t="n">
-        <v>12.05293938203411</v>
+        <v>12.2618222170032</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581623964167513</v>
+        <v>0.7582057203946972</v>
       </c>
       <c r="G18" t="n">
-        <v>21.84533656882982</v>
+        <v>22.59405356075014</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17994928671355</v>
+        <v>36.9754170922549</v>
       </c>
       <c r="I18" t="n">
-        <v>1.719836926616469</v>
+        <v>1.796340623423582</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738514977604696</v>
+        <v>4.738785752466857</v>
       </c>
       <c r="K18" t="n">
-        <v>20.42249245832891</v>
+        <v>19.53352972961047</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60688664670541</v>
+        <v>43.47818976924734</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94271337192097</v>
+        <v>99.94016650349542</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.64763538611668</v>
+        <v>79.56826929577413</v>
       </c>
       <c r="C19" t="n">
-        <v>35.2482004349898</v>
+        <v>36.30721758088204</v>
       </c>
       <c r="D19" t="n">
-        <v>1.249622153045975</v>
+        <v>1.309370222578698</v>
       </c>
       <c r="E19" t="n">
-        <v>11.98051107152773</v>
+        <v>12.21471226930895</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586232099496746</v>
+        <v>0.7586814999466666</v>
       </c>
       <c r="G19" t="n">
-        <v>21.28086796959019</v>
+        <v>22.04723662965165</v>
       </c>
       <c r="H19" t="n">
-        <v>37.20254737897675</v>
+        <v>36.9986194328662</v>
       </c>
       <c r="I19" t="n">
-        <v>1.434068540840896</v>
+        <v>1.497889866755289</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741395062185466</v>
+        <v>4.741759374666665</v>
       </c>
       <c r="K19" t="n">
-        <v>21.35236461388332</v>
+        <v>20.43173070422588</v>
       </c>
       <c r="L19" t="n">
-        <v>43.35166170316531</v>
+        <v>43.21115336424141</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95222675203843</v>
+        <v>99.95010164934934</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.21720113452919</v>
+        <v>77.06389962457982</v>
       </c>
       <c r="C20" t="n">
-        <v>33.03836633875397</v>
+        <v>34.03367120956322</v>
       </c>
       <c r="D20" t="n">
-        <v>1.162225063582332</v>
+        <v>1.217842614457682</v>
       </c>
       <c r="E20" t="n">
-        <v>11.34188869491239</v>
+        <v>11.56903199556874</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590199148657922</v>
+        <v>0.7590913457010074</v>
       </c>
       <c r="G20" t="n">
-        <v>19.79250933472704</v>
+        <v>20.50609051253902</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22200161296772</v>
+        <v>37.01860638007936</v>
       </c>
       <c r="I20" t="n">
-        <v>1.195682045562706</v>
+        <v>1.2489158656027</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743874467911202</v>
+        <v>4.744320910631296</v>
       </c>
       <c r="K20" t="n">
-        <v>23.78279886547082</v>
+        <v>22.9361003754202</v>
       </c>
       <c r="L20" t="n">
-        <v>43.13899955852963</v>
+        <v>42.98862036316227</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96016476275443</v>
+        <v>99.95839194814569</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.08398797042953</v>
+        <v>82.80423735617318</v>
       </c>
       <c r="C21" t="n">
-        <v>36.66800628387855</v>
+        <v>37.53798448291584</v>
       </c>
       <c r="D21" t="n">
-        <v>1.163042349372529</v>
+        <v>1.218751731301627</v>
       </c>
       <c r="E21" t="n">
-        <v>13.30162142120799</v>
+        <v>13.47646633324736</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595536636295511</v>
+        <v>0.7596580057277439</v>
       </c>
       <c r="G21" t="n">
-        <v>21.46957407959487</v>
+        <v>22.11113043582668</v>
       </c>
       <c r="H21" t="n">
-        <v>38.91132291365741</v>
+        <v>38.63597286029061</v>
       </c>
       <c r="I21" t="n">
-        <v>1.731663145282482</v>
+        <v>1.85439545398075</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747210397684696</v>
+        <v>4.747862535798398</v>
       </c>
       <c r="K21" t="n">
-        <v>17.91601202957047</v>
+        <v>17.19576264382684</v>
       </c>
       <c r="L21" t="n">
-        <v>45.35830014382198</v>
+        <v>45.20448580044252</v>
       </c>
       <c r="M21" t="n">
-        <v>99.942318457271</v>
+        <v>99.9382329271852</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_69_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_69_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.79724235780715</v>
+        <v>43.53196708368357</v>
       </c>
       <c r="M2" t="n">
-        <v>101.8701008820861</v>
+        <v>96.34801685850854</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0537715092111</v>
+        <v>81.56516926486876</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93486515232468</v>
+        <v>43.32072482042432</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22879379271933</v>
+        <v>2.18523561504944</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711345717480888</v>
+        <v>4.15434770188731</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429312642397768</v>
+        <v>0.7376952145990717</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97498852593531</v>
+        <v>32.86958570970199</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17483815502973</v>
+        <v>33.93397987155729</v>
       </c>
       <c r="I3" t="n">
-        <v>6.577553652307477</v>
+        <v>3.073730060829465</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643320401498605</v>
+        <v>4.610595091244198</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94622849078888</v>
+        <v>18.43483073513124</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88281260343849</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639062465521</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.2189892816767</v>
+        <v>88.76155669001236</v>
       </c>
       <c r="C4" t="n">
-        <v>42.73682619121693</v>
+        <v>42.92296343285809</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188990692124298</v>
+        <v>2.191043677525147</v>
       </c>
       <c r="E4" t="n">
-        <v>6.524816046659398</v>
+        <v>6.547922715551258</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444908534264624</v>
+        <v>0.7396559093016998</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36824334814885</v>
+        <v>33.55842459660311</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24657925761727</v>
+        <v>34.02417182787818</v>
       </c>
       <c r="I4" t="n">
-        <v>5.492801249785026</v>
+        <v>7.077488530017312</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65306783391539</v>
+        <v>4.622849433135624</v>
       </c>
       <c r="K4" t="n">
-        <v>12.7810107183233</v>
+        <v>11.23844330998768</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29945326678457</v>
+        <v>45.60330234443317</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8172901763248</v>
+        <v>99.76470908727893</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12129015230245</v>
+        <v>87.81144229592314</v>
       </c>
       <c r="C5" t="n">
-        <v>42.49173087345491</v>
+        <v>43.06991702295001</v>
       </c>
       <c r="D5" t="n">
-        <v>2.135675144145167</v>
+        <v>2.146632875084114</v>
       </c>
       <c r="E5" t="n">
-        <v>7.130139207217817</v>
+        <v>7.400391475838461</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458121804854116</v>
+        <v>0.7413156059074016</v>
       </c>
       <c r="G5" t="n">
-        <v>32.55551893337253</v>
+        <v>32.87822064618462</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30736030232894</v>
+        <v>34.10051787174047</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585458256718764</v>
+        <v>5.911141284246809</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661326128033823</v>
+        <v>4.63322253692126</v>
       </c>
       <c r="K5" t="n">
-        <v>13.87870984769755</v>
+        <v>12.18855770407684</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47698146635352</v>
+        <v>44.54492836936157</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84742218750598</v>
+        <v>99.80340309638842</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.91994552158431</v>
+        <v>86.74839521822211</v>
       </c>
       <c r="C6" t="n">
-        <v>42.00267003682482</v>
+        <v>42.92450537034784</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077442520499378</v>
+        <v>2.096813684080331</v>
       </c>
       <c r="E6" t="n">
-        <v>7.573550369699363</v>
+        <v>8.051191499138632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469325258153166</v>
+        <v>0.7427214376623732</v>
       </c>
       <c r="G6" t="n">
-        <v>31.6678402586276</v>
+        <v>32.11518083008535</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35889618750456</v>
+        <v>34.16518613246916</v>
       </c>
       <c r="I6" t="n">
-        <v>3.826955373092354</v>
+        <v>4.935292649396435</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668328286345729</v>
+        <v>4.642008985389833</v>
       </c>
       <c r="K6" t="n">
-        <v>15.08005447841571</v>
+        <v>13.25160478177787</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78990164429506</v>
+        <v>43.65969147886741</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87262615953559</v>
+        <v>99.83580163099313</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.54438517833</v>
+        <v>85.47560926665059</v>
       </c>
       <c r="C7" t="n">
-        <v>41.22172691098353</v>
+        <v>42.41857881181133</v>
       </c>
       <c r="D7" t="n">
-        <v>2.010840275811118</v>
+        <v>2.036933615887475</v>
       </c>
       <c r="E7" t="n">
-        <v>7.862943160422263</v>
+        <v>8.507826862674561</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478841554594061</v>
+        <v>0.7439145772988085</v>
       </c>
       <c r="G7" t="n">
-        <v>30.65257787478709</v>
+        <v>31.19804678392194</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40267115113269</v>
+        <v>34.22007055574518</v>
       </c>
       <c r="I7" t="n">
-        <v>3.193192589096157</v>
+        <v>4.119350763005072</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674275971621289</v>
+        <v>4.649466108117553</v>
       </c>
       <c r="K7" t="n">
-        <v>16.45561482166999</v>
+        <v>14.5243907333494</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21635395142725</v>
+        <v>42.91993899235602</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89369568408077</v>
+        <v>99.86290853751674</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.48551641133636</v>
+        <v>83.99682441892355</v>
       </c>
       <c r="C8" t="n">
-        <v>43.5428680803285</v>
+        <v>41.58006904247311</v>
       </c>
       <c r="D8" t="n">
-        <v>2.015149442677872</v>
+        <v>1.967453206522662</v>
       </c>
       <c r="E8" t="n">
-        <v>9.711485418434556</v>
+        <v>8.790534879081413</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749486847459185</v>
+        <v>0.7449293727327696</v>
       </c>
       <c r="G8" t="n">
-        <v>31.16005735556413</v>
+        <v>30.13387216133117</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47639498312252</v>
+        <v>34.26675114570739</v>
       </c>
       <c r="I8" t="n">
-        <v>5.688649567458183</v>
+        <v>3.437475073968348</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684292796619907</v>
+        <v>4.655808579579809</v>
       </c>
       <c r="K8" t="n">
-        <v>11.51448358866364</v>
+        <v>16.00317558107644</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75343216299968</v>
+        <v>42.30232896636696</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81078383199181</v>
+        <v>99.8855735899165</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.68747545727702</v>
+        <v>82.37074110710336</v>
       </c>
       <c r="C9" t="n">
-        <v>42.62822832777891</v>
+        <v>40.48813340145454</v>
       </c>
       <c r="D9" t="n">
-        <v>1.93418926446663</v>
+        <v>1.891409090438317</v>
       </c>
       <c r="E9" t="n">
-        <v>10.11285208677934</v>
+        <v>8.928752724879553</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508555425698984</v>
+        <v>0.7457939084000013</v>
       </c>
       <c r="G9" t="n">
-        <v>29.90817809383225</v>
+        <v>28.96916660944812</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53935495821533</v>
+        <v>34.30651978640005</v>
       </c>
       <c r="I9" t="n">
-        <v>4.749198370351698</v>
+        <v>2.867887060037325</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692847141061866</v>
+        <v>4.661211927500007</v>
       </c>
       <c r="K9" t="n">
-        <v>13.312524542723</v>
+        <v>17.62925889289663</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90122908595757</v>
+        <v>41.78712228692749</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84198195645948</v>
+        <v>99.90451458127866</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.70708658445668</v>
+        <v>86.64096628923195</v>
       </c>
       <c r="C10" t="n">
-        <v>41.38529699959889</v>
+        <v>43.37835964374909</v>
       </c>
       <c r="D10" t="n">
-        <v>1.845765386184198</v>
+        <v>1.893612510660975</v>
       </c>
       <c r="E10" t="n">
-        <v>10.31117018149147</v>
+        <v>10.61476281363721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520267433408087</v>
+        <v>0.7466627301625754</v>
       </c>
       <c r="G10" t="n">
-        <v>28.54088837301602</v>
+        <v>30.17385574149683</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59323019367721</v>
+        <v>35.51742673350792</v>
       </c>
       <c r="I10" t="n">
-        <v>3.963838560866924</v>
+        <v>3.028003696250356</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700167145880055</v>
+        <v>4.666642063516096</v>
       </c>
       <c r="K10" t="n">
-        <v>15.29291341554331</v>
+        <v>13.35903371076805</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18986740790362</v>
+        <v>43.16179063578844</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86807782304582</v>
+        <v>99.89918399030557</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.61107574919902</v>
+        <v>86.57750611762944</v>
       </c>
       <c r="C11" t="n">
-        <v>39.90437298222854</v>
+        <v>43.74430359492563</v>
       </c>
       <c r="D11" t="n">
-        <v>1.753041671255363</v>
+        <v>1.888714170482839</v>
       </c>
       <c r="E11" t="n">
-        <v>10.34444698274354</v>
+        <v>11.0333637779304</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530304058283068</v>
+        <v>0.7473943520756818</v>
       </c>
       <c r="G11" t="n">
-        <v>27.10711070163696</v>
+        <v>30.11769441025964</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63939866810212</v>
+        <v>35.57412019102368</v>
       </c>
       <c r="I11" t="n">
-        <v>3.307607283205793</v>
+        <v>2.545004515384182</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706440036426918</v>
+        <v>4.671214700473011</v>
       </c>
       <c r="K11" t="n">
-        <v>17.388924250801</v>
+        <v>13.42249388237056</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5965961402797</v>
+        <v>42.74845208208053</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88989337330923</v>
+        <v>99.91524955937672</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.30268323661591</v>
+        <v>85.02229994437801</v>
       </c>
       <c r="C12" t="n">
-        <v>38.10862714932632</v>
+        <v>42.58543338685602</v>
       </c>
       <c r="D12" t="n">
-        <v>1.651711226869334</v>
+        <v>1.821982010247039</v>
       </c>
       <c r="E12" t="n">
-        <v>10.20642670357129</v>
+        <v>10.99729932002921</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538929693247318</v>
+        <v>0.7480163146861784</v>
       </c>
       <c r="G12" t="n">
-        <v>25.54024802035729</v>
+        <v>29.05357425871521</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67907658893768</v>
+        <v>35.60372407095491</v>
       </c>
       <c r="I12" t="n">
-        <v>2.759496669276004</v>
+        <v>2.122602002956833</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711831058279574</v>
+        <v>4.675101966788614</v>
       </c>
       <c r="K12" t="n">
-        <v>19.6973167633841</v>
+        <v>14.97770005562202</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10217810720054</v>
+        <v>42.36617198765018</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90812201991096</v>
+        <v>99.92930543012821</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.82936165350294</v>
+        <v>86.20722033601865</v>
       </c>
       <c r="C13" t="n">
-        <v>36.06222076329802</v>
+        <v>43.5711246842849</v>
       </c>
       <c r="D13" t="n">
-        <v>1.543996871547371</v>
+        <v>1.823378832274936</v>
       </c>
       <c r="E13" t="n">
-        <v>9.924468164773362</v>
+        <v>11.64644789934743</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546361964259152</v>
+        <v>0.7485897811966616</v>
       </c>
       <c r="G13" t="n">
-        <v>23.87467155304092</v>
+        <v>29.38611196272008</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71326503559211</v>
+        <v>35.94128344558678</v>
       </c>
       <c r="I13" t="n">
-        <v>2.301847604461306</v>
+        <v>1.982722282413636</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716476227661969</v>
+        <v>4.678686132479134</v>
       </c>
       <c r="K13" t="n">
-        <v>22.17063834649706</v>
+        <v>13.79277966398133</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69048820494725</v>
+        <v>42.57005553862198</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92334731474233</v>
+        <v>99.93395988688822</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.23825659281238</v>
+        <v>84.62127564214724</v>
       </c>
       <c r="C14" t="n">
-        <v>39.96634910324666</v>
+        <v>42.29396187644736</v>
       </c>
       <c r="D14" t="n">
-        <v>1.545869254685917</v>
+        <v>1.757045687060828</v>
       </c>
       <c r="E14" t="n">
-        <v>12.12852362110706</v>
+        <v>11.49831635906583</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555513330534321</v>
+        <v>0.7490773169441848</v>
       </c>
       <c r="G14" t="n">
-        <v>25.58487151991561</v>
+        <v>28.3170673968856</v>
       </c>
       <c r="H14" t="n">
-        <v>36.43660881127643</v>
+        <v>35.96469100595125</v>
       </c>
       <c r="I14" t="n">
-        <v>3.064636221189994</v>
+        <v>1.653344645338403</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72219583158395</v>
+        <v>4.681733230901154</v>
       </c>
       <c r="K14" t="n">
-        <v>15.76174340718761</v>
+        <v>15.37872435785276</v>
       </c>
       <c r="L14" t="n">
-        <v>44.16987668017691</v>
+        <v>42.27223814674394</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89796919061116</v>
+        <v>99.94492438104406</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.51016304291181</v>
+        <v>83.97512857312017</v>
       </c>
       <c r="C15" t="n">
-        <v>39.70867145461086</v>
+        <v>41.90139796778095</v>
       </c>
       <c r="D15" t="n">
-        <v>1.51831120843492</v>
+        <v>1.730508946317498</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34208639490023</v>
+        <v>11.55499375978951</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563223146507998</v>
+        <v>0.7494882486587077</v>
       </c>
       <c r="G15" t="n">
-        <v>25.13247115932704</v>
+        <v>27.88939344301161</v>
       </c>
       <c r="H15" t="n">
-        <v>36.47748796151946</v>
+        <v>35.98442065441751</v>
       </c>
       <c r="I15" t="n">
-        <v>2.556469537511864</v>
+        <v>1.382021966808412</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727014466567498</v>
+        <v>4.684301554116922</v>
       </c>
       <c r="K15" t="n">
-        <v>16.48983695708817</v>
+        <v>16.02487142687984</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71636280437902</v>
+        <v>42.02768846442027</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91487121607805</v>
+        <v>99.95395785908106</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.09250132895659</v>
+        <v>81.91043461127278</v>
       </c>
       <c r="C16" t="n">
-        <v>37.68659457690107</v>
+        <v>40.05163793132</v>
       </c>
       <c r="D16" t="n">
-        <v>1.425420116115933</v>
+        <v>1.644504206978263</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94236736204267</v>
+        <v>11.17275845382467</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569852097662545</v>
+        <v>0.7498396809258683</v>
       </c>
       <c r="G16" t="n">
-        <v>23.59485312311967</v>
+        <v>26.50331565445131</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50945944791533</v>
+        <v>36.00129361614263</v>
       </c>
       <c r="I16" t="n">
-        <v>2.132258508957653</v>
+        <v>1.152224993163363</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73115756103909</v>
+        <v>4.686498005786675</v>
       </c>
       <c r="K16" t="n">
-        <v>18.90749867104341</v>
+        <v>18.08956538872722</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33489370934685</v>
+        <v>41.82040718087477</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92898695729133</v>
+        <v>99.96161050092199</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.76212037966097</v>
+        <v>85.90504821012856</v>
       </c>
       <c r="C17" t="n">
-        <v>38.89118961823893</v>
+        <v>42.61853008273378</v>
       </c>
       <c r="D17" t="n">
-        <v>1.426656737930027</v>
+        <v>1.645394461806476</v>
       </c>
       <c r="E17" t="n">
-        <v>12.71851853867714</v>
+        <v>12.56981466680982</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576419315374434</v>
+        <v>0.7502456077660049</v>
       </c>
       <c r="G17" t="n">
-        <v>24.0221124232415</v>
+        <v>27.67614695177304</v>
       </c>
       <c r="H17" t="n">
-        <v>36.9479228020007</v>
+        <v>37.17926665813293</v>
       </c>
       <c r="I17" t="n">
-        <v>2.15400587416513</v>
+        <v>1.395144815302738</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735262072109021</v>
+        <v>4.689035048537529</v>
       </c>
       <c r="K17" t="n">
-        <v>17.23787962033903</v>
+        <v>14.09495178987146</v>
       </c>
       <c r="L17" t="n">
-        <v>43.79919280181256</v>
+        <v>43.24003846205482</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92826204039052</v>
+        <v>99.95352033466006</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.46647027038951</v>
+        <v>87.48924539308641</v>
       </c>
       <c r="C18" t="n">
-        <v>36.9284470046376</v>
+        <v>43.35445937811219</v>
       </c>
       <c r="D18" t="n">
-        <v>1.341845304096138</v>
+        <v>1.646770623494936</v>
       </c>
       <c r="E18" t="n">
-        <v>12.2618222170032</v>
+        <v>13.17791955294727</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582057203946972</v>
+        <v>0.7508730921087009</v>
       </c>
       <c r="G18" t="n">
-        <v>22.59405356075014</v>
+        <v>27.8151565610244</v>
       </c>
       <c r="H18" t="n">
-        <v>36.9754170922549</v>
+        <v>37.21036235194228</v>
       </c>
       <c r="I18" t="n">
-        <v>1.796340623423582</v>
+        <v>2.195206385889442</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738785752466857</v>
+        <v>4.69295682567938</v>
       </c>
       <c r="K18" t="n">
-        <v>19.53352972961047</v>
+        <v>12.51075460691359</v>
       </c>
       <c r="L18" t="n">
-        <v>43.47818976924734</v>
+        <v>44.06167361793215</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94016650349542</v>
+        <v>99.92688760295793</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.56826929577413</v>
+        <v>85.29482328959983</v>
       </c>
       <c r="C19" t="n">
-        <v>36.30721758088204</v>
+        <v>41.50118750190673</v>
       </c>
       <c r="D19" t="n">
-        <v>1.309370222578698</v>
+        <v>1.563138526132307</v>
       </c>
       <c r="E19" t="n">
-        <v>12.21471226930895</v>
+        <v>12.81377999643201</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586814999466666</v>
+        <v>0.7514102813621539</v>
       </c>
       <c r="G19" t="n">
-        <v>22.04723662965165</v>
+        <v>26.40254945686596</v>
       </c>
       <c r="H19" t="n">
-        <v>36.9986194328662</v>
+        <v>37.236983370837</v>
       </c>
       <c r="I19" t="n">
-        <v>1.497889866755289</v>
+        <v>1.830647399456941</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741759374666665</v>
+        <v>4.696314258513461</v>
       </c>
       <c r="K19" t="n">
-        <v>20.43173070422588</v>
+        <v>14.70517671040015</v>
       </c>
       <c r="L19" t="n">
-        <v>43.21115336424141</v>
+        <v>43.73265783252953</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95010164934934</v>
+        <v>99.93902204483642</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.06389962457982</v>
+        <v>82.97325504093631</v>
       </c>
       <c r="C20" t="n">
-        <v>34.03367120956322</v>
+        <v>39.46356659538679</v>
       </c>
       <c r="D20" t="n">
-        <v>1.217842614457682</v>
+        <v>1.475053319925238</v>
       </c>
       <c r="E20" t="n">
-        <v>11.56903199556874</v>
+        <v>12.34611673096219</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590913457010074</v>
+        <v>0.7518710760381002</v>
       </c>
       <c r="G20" t="n">
-        <v>20.50609051253902</v>
+        <v>24.91472609737472</v>
       </c>
       <c r="H20" t="n">
-        <v>37.01860638007936</v>
+        <v>37.25981857034275</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2489158656027</v>
+        <v>1.526475021055172</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744320910631296</v>
+        <v>4.699194225238126</v>
       </c>
       <c r="K20" t="n">
-        <v>22.9361003754202</v>
+        <v>17.02674495906371</v>
       </c>
       <c r="L20" t="n">
-        <v>42.98862036316227</v>
+        <v>43.4588371288979</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95839194814569</v>
+        <v>99.9491486833484</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.80423735617318</v>
+        <v>80.642271831789</v>
       </c>
       <c r="C21" t="n">
-        <v>37.53798448291584</v>
+        <v>37.36879443474396</v>
       </c>
       <c r="D21" t="n">
-        <v>1.218751731301627</v>
+        <v>1.38701935860817</v>
       </c>
       <c r="E21" t="n">
-        <v>13.47646633324736</v>
+        <v>11.82139917714602</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596580057277439</v>
+        <v>0.7522666213480561</v>
       </c>
       <c r="G21" t="n">
-        <v>22.11113043582668</v>
+        <v>23.42776830144039</v>
       </c>
       <c r="H21" t="n">
-        <v>38.63597286029061</v>
+        <v>37.27942026397747</v>
       </c>
       <c r="I21" t="n">
-        <v>1.85439545398075</v>
+        <v>1.272731725843545</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747862535798398</v>
+        <v>4.70166638342535</v>
       </c>
       <c r="K21" t="n">
-        <v>17.19576264382684</v>
+        <v>19.35772816821099</v>
       </c>
       <c r="L21" t="n">
-        <v>45.20448580044252</v>
+        <v>43.23107531312685</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9382329271852</v>
+        <v>99.95759791608181</v>
       </c>
     </row>
   </sheetData>
